--- a/models/sovereigns/Bahrain_Sovereign_Model.xlsx
+++ b/models/sovereigns/Bahrain_Sovereign_Model.xlsx
@@ -688,16 +688,34 @@
           <t>real_gdp_growth_pct</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
+      <c r="B6" s="2" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -860,16 +878,34 @@
           <t>current_account_pct_gdp</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
+      <c r="B14" s="2" t="n">
+        <v>3.9</v>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -877,16 +913,34 @@
           <t>fdi_net_pct_gdp</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>1.677</v>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -894,16 +948,34 @@
           <t>gross_reserves_usd_bn</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n"/>
+      <c r="B16" s="2" t="n">
+        <v>5.27</v>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1014,16 +1086,34 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>48.849</v>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/models/sovereigns/Bahrain_Sovereign_Model.xlsx
+++ b/models/sovereigns/Bahrain_Sovereign_Model.xlsx
@@ -671,16 +671,34 @@
           <t>cpi_latest_yoy_pct</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
+      <c r="B5" s="2" t="n">
+        <v>2.9329</v>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>IMF CPI database</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>IMF CPI database, all items, y/y % change, monthly (auto-filled; a run's sourced point replaces it unless older)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -741,7 +759,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -750,12 +768,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>end-2024</t>
+          <t>2026F</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF Article IV</t>
+          <t>IMF 2025 Article IV</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -765,7 +783,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>gross government debt; above 133% across 2025-2026</t>
+          <t>Gross government debt; projected 'above 133%' for 2026 (lower bound as stated)</t>
         </is>
       </c>
     </row>
@@ -793,7 +811,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-11</v>
+        <v>10.8</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -802,12 +820,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025E</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMF Article IV</t>
+          <t>IMF 2025 Article IV (deficit; sign negative)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -815,11 +833,7 @@
           <t>23-Jan-26</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2025 estimated -10.8 to -11.0</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -844,15 +858,29 @@
           <t>interest_pct_revenue</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n"/>
+      <c r="B12" s="2" t="n">
+        <v>27.5</v>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Rating Agencies / IMF (stated range ~25-30%; midpoint)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>23-Jan-26</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -949,7 +977,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>5.27</v>
+        <v>6.671</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -958,12 +986,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>World Bank WDI</t>
+          <t>IMF International Liquidity</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -973,7 +1001,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+          <t>Gross official reserves incl. gold at national valuation, end-month (auto-filled; a run's sourced point replaces it unless older)</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1038,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025-26</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IMF Article IV</t>
+          <t>IMF Article IV (gross reserves vs prospective non-hydrocarbon imports; 'barely/slightly over two months')</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1023,11 +1051,7 @@
           <t>23-Jan-26</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>slightly over two months of prospective non-hydrocarbon imports</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1275,11 +1299,6 @@
       <c r="A33" t="inlineStr">
         <is>
           <t>IMF</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>None (Article IV)</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1318,6 +1337,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>2026F</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
@@ -1330,7 +1354,8 @@
       </c>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1340,7 +1365,8 @@
       </c>
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="n"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1350,7 +1376,8 @@
       </c>
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="n"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1360,7 +1387,8 @@
       </c>
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1372,11 +1400,12 @@
         <v>-11</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-10.9</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>IMF Article IV, 23-Jan-26 (2025 given as 10.8-11.0)</t>
+        <v>-10.8</v>
+      </c>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>IMF 2025 Article IV, 23-Jan-26</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1417,8 @@
       </c>
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="n"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1399,8 +1429,17 @@
       <c r="B8" s="2" t="n">
         <v>134</v>
       </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="C8" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>IMF 2025 Article IV, 23-Jan-26 (2025E/2026F shown as lower bound 'above 133%')</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1410,7 +1449,8 @@
       </c>
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="n"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1420,7 +1460,8 @@
       </c>
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="n"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1430,7 +1471,8 @@
       </c>
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="n"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1440,7 +1482,8 @@
       </c>
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="n"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/sovereigns/Bahrain_Sovereign_Model.xlsx
+++ b/models/sovereigns/Bahrain_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/bahrain.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/bahrain.json</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -768,12 +768,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026F</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF 2025 Article IV</t>
+          <t>IMF Article IV</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gross government debt; projected 'above 133%' for 2026 (lower bound as stated)</t>
+          <t>gross government debt</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>10.8</v>
+        <v>-11</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -820,12 +820,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025E</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMF 2025 Article IV (deficit; sign negative)</t>
+          <t>IMF Article IV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1405,7 +1405,7 @@
       <c r="D6" s="2" t="n"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF 2025 Article IV, 23-Jan-26</t>
+          <t>IMF Article IV, 23-Jan-26 (2025E is the ~10.8% point estimate within a 10.8-11.0% range)</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF 2025 Article IV, 23-Jan-26 (2025E/2026F shown as lower bound 'above 133%')</t>
+          <t>IMF Article IV, 23-Jan-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Bahrain_Sovereign_Model.xlsx
+++ b/models/sovereigns/Bahrain_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -768,12 +768,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026E</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF Article IV</t>
+          <t>IMF 2025 Article IV</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>gross government debt</t>
+          <t>Gross government debt; floor of projection 'above 133%' for 2025-2026</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-11</v>
+        <v>10.8</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -820,12 +820,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025E</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMF Article IV</t>
+          <t>IMF 2025 Article IV (deficit, 10.8-11.0% range; sign shown as deficit magnitude, balance is -10.8)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -868,12 +868,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-26</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rating Agencies / IMF (stated range ~25-30%; midpoint)</t>
+          <t>Rating Agencies / IMF (interest absorbs ~25-30% of revenue; midpoint)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-26</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IMF Article IV (gross reserves vs prospective non-hydrocarbon imports; 'barely/slightly over two months')</t>
+          <t>Central Bank of Bahrain / IMF (approx. two months of prospective non-hydrocarbon imports)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1337,10 +1337,15 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>2026F</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -1355,7 +1360,8 @@
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1366,7 +1372,8 @@
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1377,7 +1384,8 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1388,7 +1396,8 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1403,9 +1412,10 @@
         <v>-10.8</v>
       </c>
       <c r="D6" s="2" t="n"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>IMF Article IV, 23-Jan-26 (2025E is the ~10.8% point estimate within a 10.8-11.0% range)</t>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>IMF 2025 Article IV, 23-Jan-26</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1428,8 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1435,9 +1446,12 @@
       <c r="D8" s="2" t="n">
         <v>133</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>IMF Article IV, 23-Jan-26</t>
+      <c r="E8" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>IMF 2025 Article IV, 23-Jan-26 (2025E and 2026E shown as 133, the 'above 133%' floor)</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1464,8 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1461,7 +1476,8 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1472,7 +1488,8 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1483,7 +1500,8 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/sovereigns/Bahrain_Sovereign_Model.xlsx
+++ b/models/sovereigns/Bahrain_Sovereign_Model.xlsx
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gross government debt; floor of projection 'above 133%' for 2025-2026</t>
+          <t>gross government debt</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>10.8</v>
+        <v>-11</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -820,12 +820,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025E</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMF 2025 Article IV (deficit, 10.8-11.0% range; sign shown as deficit magnitude, balance is -10.8)</t>
+          <t>IMF 2025 Article IV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1415,7 +1415,7 @@
       <c r="E6" s="2" t="n"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>IMF 2025 Article IV, 23-Jan-26</t>
+          <t>IMF 2025 Article IV, 23-Jan-26 (2025E is the low end of the 10.8-11.0% range given)</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IMF 2025 Article IV, 23-Jan-26 (2025E and 2026E shown as 133, the 'above 133%' floor)</t>
+          <t>IMF 2025 Article IV, 23-Jan-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Bahrain_Sovereign_Model.xlsx
+++ b/models/sovereigns/Bahrain_Sovereign_Model.xlsx
@@ -825,7 +825,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMF 2025 Article IV</t>
+          <t>IMF 2025 Article IV (central government headline deficit)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1415,7 +1415,7 @@
       <c r="E6" s="2" t="n"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>IMF 2025 Article IV, 23-Jan-26 (2025E is the low end of the 10.8-11.0% range given)</t>
+          <t>IMF 2025 Article IV, 23-Jan-26 (2025E quoted as ~10.8%, range 10.8-11.0%)</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IMF 2025 Article IV, 23-Jan-26</t>
+          <t>IMF 2025 Article IV, 23-Jan-26 (2025-26 projected above 133%, not stored as a point value)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Bahrain_Sovereign_Model.xlsx
+++ b/models/sovereigns/Bahrain_Sovereign_Model.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF 2025 Article IV</t>
+          <t>IMF 2025 Article IV, concluded 23-Jan-26</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMF 2025 Article IV (central government headline deficit)</t>
+          <t>IMF 2025 Article IV, concluded 23-Jan-26</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1332,20 +1332,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>2025E</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2026E</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2026F</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -1361,7 +1366,8 @@
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1373,7 +1379,8 @@
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1385,7 +1392,8 @@
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1397,7 +1405,8 @@
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="n"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1411,11 +1420,14 @@
       <c r="C6" s="2" t="n">
         <v>-10.8</v>
       </c>
-      <c r="D6" s="2" t="n"/>
+      <c r="D6" s="2" t="n">
+        <v>-10.8</v>
+      </c>
       <c r="E6" s="2" t="n"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>IMF 2025 Article IV, 23-Jan-26 (2025E quoted as ~10.8%, range 10.8-11.0%)</t>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>IMF 2025 Article IV, 23-Jan-26; 2025 is the ~10.8% figure from a stated 10.8%-11.0% range</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1441,8 @@
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1440,18 +1453,19 @@
       <c r="B8" s="2" t="n">
         <v>134</v>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>133</v>
-      </c>
+      <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
         <v>133</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>133</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>IMF 2025 Article IV, 23-Jan-26 (2025-26 projected above 133%, not stored as a point value)</t>
+      <c r="F8" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>IMF 2025 Article IV, 23-Jan-26; gross government debt, 2025-2026 stated only as above 133%</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1479,8 @@
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1477,7 +1492,8 @@
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="n"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1489,7 +1505,8 @@
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="n"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1501,7 +1518,8 @@
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="n"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/sovereigns/Bahrain_Sovereign_Model.xlsx
+++ b/models/sovereigns/Bahrain_Sovereign_Model.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF 2025 Article IV, concluded 23-Jan-26</t>
+          <t>IMF 2025 Article IV consultation</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>gross government debt</t>
+          <t>Gross government debt</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-11</v>
+        <v>-10.8</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -820,12 +820,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025E</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMF 2025 Article IV, concluded 23-Jan-26</t>
+          <t>IMF 2025 Article IV consultation (document range 10.8-11.0% deficit)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1427,7 +1427,7 @@
       <c r="F6" s="2" t="n"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>IMF 2025 Article IV, 23-Jan-26; 2025 is the ~10.8% figure from a stated 10.8%-11.0% range</t>
+          <t>IMF 2025 Article IV consultation, 23-Jan-26</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>IMF 2025 Article IV, 23-Jan-26; gross government debt, 2025-2026 stated only as above 133%</t>
+          <t>IMF 2025 Article IV consultation, 23-Jan-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Bahrain_Sovereign_Model.xlsx
+++ b/models/sovereigns/Bahrain_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/bahrain.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/bahrain.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Bahrain_Sovereign_Model.xlsx
+++ b/models/sovereigns/Bahrain_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/bahrain.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/bahrain.json</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>19-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">

--- a/models/sovereigns/Bahrain_Sovereign_Model.xlsx
+++ b/models/sovereigns/Bahrain_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/bahrain.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/bahrain.json</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19-Oct-26</t>
+          <t>26-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>6.671</v>
+        <v>3.079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>26-Oct-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
